--- a/AULA 21092026/ATIVIDADE EXCEL PTIC.xlsx
+++ b/AULA 21092026/ATIVIDADE EXCEL PTIC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMARGO\Desktop\projetos_de_tecnologia_de_informacao_e_comunicacao\AULA 21092026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94DBC0E9-C7B6-48FC-8266-5BF91320A68C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596D5EF5-0D27-47C5-B844-D252CA65A982}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{1DAE4682-B86A-404A-A057-CC81811930FF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>Aluno</t>
   </si>
@@ -97,6 +97,21 @@
   </si>
   <si>
     <t>soma</t>
+  </si>
+  <si>
+    <t>Nota3</t>
+  </si>
+  <si>
+    <t>Nota4</t>
+  </si>
+  <si>
+    <t>Nota Máximo</t>
+  </si>
+  <si>
+    <t>A nota máxima</t>
+  </si>
+  <si>
+    <t>Média</t>
   </si>
 </sst>
 </file>
@@ -167,9 +182,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -177,6 +189,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -495,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4796349C-7566-4668-8BFD-F82B257C12C5}">
-  <dimension ref="B2:X19"/>
+  <dimension ref="B2:Z19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
@@ -503,10 +518,11 @@
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>18</v>
       </c>
@@ -516,55 +532,67 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="J3" s="1" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="J3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="P4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -574,21 +602,31 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>2</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>7</v>
       </c>
-      <c r="M5" s="3">
-        <f>K5+L5</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="2">
+        <v>6</v>
+      </c>
+      <c r="O5" s="2">
+        <f>SUM(K5:N5)</f>
+        <v>16</v>
+      </c>
+      <c r="P5" s="2">
+        <f>AVERAGE(K5:N5)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -598,21 +636,31 @@
       <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>8</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>5</v>
       </c>
-      <c r="M6" s="3">
-        <f t="shared" ref="M6:M9" si="0">K6+L6</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="M6" s="2">
+        <v>9</v>
+      </c>
+      <c r="N6" s="2">
+        <v>8</v>
+      </c>
+      <c r="O6" s="2">
+        <f t="shared" ref="O6:O9" si="0">SUM(K6:N6)</f>
+        <v>30</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6:P9" si="1">AVERAGE(K6:N6)</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>21</v>
       </c>
@@ -622,21 +670,31 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>9</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>8</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
+        <v>2</v>
+      </c>
+      <c r="N7" s="2">
+        <v>7</v>
+      </c>
+      <c r="O7" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="1"/>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>23</v>
       </c>
@@ -646,58 +704,94 @@
       <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>10</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
+        <v>10</v>
+      </c>
+      <c r="N8" s="2">
+        <v>8</v>
+      </c>
+      <c r="O8" s="2">
         <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="J9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" s="2">
+        <f t="shared" si="1"/>
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="J9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>6</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>3</v>
+      </c>
+      <c r="O9" s="2">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="X14" s="4"/>
-    </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="X15" s="4"/>
-    </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="X16" s="4"/>
-    </row>
-    <row r="17" spans="24:24" x14ac:dyDescent="0.25">
-      <c r="X17" s="4"/>
-    </row>
-    <row r="18" spans="24:24" x14ac:dyDescent="0.25">
-      <c r="X18" s="4"/>
-    </row>
-    <row r="19" spans="24:24" x14ac:dyDescent="0.25">
-      <c r="X19" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="P9" s="2">
+        <f t="shared" si="1"/>
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13">
+        <f>MAX(K5:N9)</f>
+        <v>10</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13">
+        <f>MAX(O5:O9)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Z14" s="3"/>
+    </row>
+    <row r="15" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Z15" s="3"/>
+    </row>
+    <row r="16" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z17" s="3"/>
+    </row>
+    <row r="18" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z18" s="3"/>
+    </row>
+    <row r="19" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z19" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="J3:M3"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
+    <mergeCell ref="J3:P3"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/AULA 21092026/ATIVIDADE EXCEL PTIC.xlsx
+++ b/AULA 21092026/ATIVIDADE EXCEL PTIC.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMARGO\Desktop\projetos_de_tecnologia_de_informacao_e_comunicacao\AULA 21092026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596D5EF5-0D27-47C5-B844-D252CA65A982}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C61D850-CFF1-4F41-A087-08CFCD125D93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{1DAE4682-B86A-404A-A057-CC81811930FF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{1DAE4682-B86A-404A-A057-CC81811930FF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="ALunos" sheetId="1" r:id="rId1"/>
+    <sheet name="Comissão" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Aluno</t>
   </si>
@@ -112,13 +113,89 @@
   </si>
   <si>
     <t>Média</t>
+  </si>
+  <si>
+    <t>Situação</t>
+  </si>
+  <si>
+    <t>Nome do vendedor</t>
+  </si>
+  <si>
+    <t>departamento</t>
+  </si>
+  <si>
+    <t>valor da venda</t>
+  </si>
+  <si>
+    <t>limite mínimo</t>
+  </si>
+  <si>
+    <t>porcentagem da comissão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor da comissão </t>
+  </si>
+  <si>
+    <t>Ana</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>Eduardo</t>
+  </si>
+  <si>
+    <t>Confecção</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Infantil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maiores valores pagos: </t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Paulo</t>
+  </si>
+  <si>
+    <t>Joana</t>
+  </si>
+  <si>
+    <t>COMISSÃO DE VENDAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,7 +204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +226,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC9C9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -177,10 +296,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,18 +310,45 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFC9C9"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -211,6 +358,1076 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>ALunos!$P$5:$P$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-418D-4C6E-B6E2-0F05D90A83A9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+          </c:dPt>
+          <c:val>
+            <c:numRef>
+              <c:f>ALunos!$J$4:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-418D-4C6E-B6E2-0F05D90A83A9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2C4C4C0-112E-407F-8C93-BA44F506A925}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,36 +1737,38 @@
     <col min="9" max="9" width="9.140625" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="J3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -591,6 +1810,9 @@
       <c r="P4" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="Q4" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -621,9 +1843,13 @@
         <f>SUM(K5:N5)</f>
         <v>16</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="7">
         <f>AVERAGE(K5:N5)</f>
         <v>4</v>
+      </c>
+      <c r="Q5" s="7" t="str">
+        <f>IF(P5&gt;=7, "APROVADO",IF(P5&gt;=5,"RECUPERAÇÃO","REPROVADO"))</f>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.25">
@@ -655,9 +1881,13 @@
         <f t="shared" ref="O6:O9" si="0">SUM(K6:N6)</f>
         <v>30</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="8">
         <f t="shared" ref="P6:P9" si="1">AVERAGE(K6:N6)</f>
         <v>7.5</v>
+      </c>
+      <c r="Q6" s="8" t="str">
+        <f t="shared" ref="Q6:Q9" si="2">IF(P6&gt;=7, "APROVADO",IF(P6&gt;=5,"RECUPERAÇÃO","REPROVADO"))</f>
+        <v>APROVADO</v>
       </c>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
@@ -689,9 +1919,13 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="9">
         <f t="shared" si="1"/>
         <v>6.5</v>
+      </c>
+      <c r="Q7" s="9" t="str">
+        <f t="shared" si="2"/>
+        <v>RECUPERAÇÃO</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
@@ -723,9 +1957,13 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="8">
         <f t="shared" si="1"/>
         <v>7.75</v>
+      </c>
+      <c r="Q8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>APROVADO</v>
       </c>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.25">
@@ -748,9 +1986,22 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="7">
         <f t="shared" si="1"/>
         <v>3.75</v>
+      </c>
+      <c r="Q9" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>REPROVADO</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <f>MAX(O5:O9)</f>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.25">
@@ -760,13 +2011,6 @@
       <c r="K13">
         <f>MAX(K5:N9)</f>
         <v>10</v>
-      </c>
-      <c r="M13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13">
-        <f>MAX(O5:O9)</f>
-        <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.25">
@@ -791,7 +2035,282 @@
   <mergeCells count="3">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="J3:Q3"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA756AE-82FC-4C95-A2FA-F0FCFE232BEC}">
+  <dimension ref="B2:G19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="14">
+        <v>13000</v>
+      </c>
+      <c r="E4" s="14">
+        <v>10000</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="G4" s="14">
+        <f>IF(D4&gt;=E4, (F4*D4),IF(D4&lt;=E4,"0"))</f>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="16">
+        <v>24000</v>
+      </c>
+      <c r="E5" s="16">
+        <v>15000</v>
+      </c>
+      <c r="F5" s="17">
+        <v>0.03</v>
+      </c>
+      <c r="G5" s="16">
+        <f t="shared" ref="G5:G12" si="0">IF(D5&gt;=E5, (F5*D5),IF(D5&lt;=E5,"0"))</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="14">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="14">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G6" s="14">
+        <f t="shared" si="0"/>
+        <v>420.00000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="14">
+        <v>12000</v>
+      </c>
+      <c r="E7" s="14">
+        <v>8000</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="14">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="14">
+        <v>9000</v>
+      </c>
+      <c r="E8" s="14">
+        <v>10000</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="G8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="19">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="19">
+        <v>6000</v>
+      </c>
+      <c r="F9" s="20">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G9" s="19">
+        <f t="shared" si="0"/>
+        <v>700.00000000000011</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="14">
+        <v>16000</v>
+      </c>
+      <c r="E10" s="14">
+        <v>15000</v>
+      </c>
+      <c r="F10" s="15">
+        <v>0.03</v>
+      </c>
+      <c r="G10" s="14">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="22">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="22">
+        <v>10000</v>
+      </c>
+      <c r="F11" s="23">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="22">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="14">
+        <v>9000</v>
+      </c>
+      <c r="E12" s="14">
+        <v>8000</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.04</v>
+      </c>
+      <c r="G12" s="14">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <f>LARGE(G4:G12, 1)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <f>LARGE(G4:G12, 2)</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <f>LARGE(G4:G12, 3)</f>
+        <v>700.00000000000011</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
